--- a/data/trans_orig/P45C_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>46330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51135</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>58401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227769</t>
+          <t>226680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248571</t>
+          <t>249607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209703</t>
+          <t>209196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233214</t>
+          <t>233387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443647</t>
+          <t>445770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476587</t>
+          <t>475447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101173</t>
+          <t>99923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>138431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83261</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>120225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194129</t>
+          <t>192982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246950</t>
+          <t>246278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353135</t>
+          <t>354644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391902</t>
+          <t>393152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385231</t>
+          <t>383724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>420688</t>
+          <t>419793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750074</t>
+          <t>750746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802895</t>
+          <t>804042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96161</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267183</t>
+          <t>266094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290258</t>
+          <t>289027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>284569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307540</t>
+          <t>306924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558097</t>
+          <t>560135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592204</t>
+          <t>591454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>67130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100069</t>
+          <t>99075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35176</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60774</t>
+          <t>60679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109313</t>
+          <t>109359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150271</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258602</t>
+          <t>259596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289480</t>
+          <t>291541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310682</t>
+          <t>310777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>336280</t>
+          <t>335782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579856</t>
+          <t>580193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620814</t>
+          <t>620768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183031</t>
+          <t>183969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197296</t>
+          <t>196981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186933</t>
+          <t>187278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200206</t>
+          <t>200100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375549</t>
+          <t>376243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393455</t>
+          <t>394474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56375</t>
+          <t>54552</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86120</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96693</t>
+          <t>96646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133568</t>
+          <t>137397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184691</t>
+          <t>186848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214436</t>
+          <t>216259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219382</t>
+          <t>220060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243153</t>
+          <t>243046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>415387</t>
+          <t>411558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452262</t>
+          <t>452309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>64423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99331</t>
+          <t>99246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>48879</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78446</t>
+          <t>78845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120310</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>166738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>515696</t>
+          <t>515781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>550060</t>
+          <t>550604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>558793</t>
+          <t>558394</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>588542</t>
+          <t>588360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1085528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1131956</t>
+          <t>1132982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61868</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97508</t>
+          <t>96083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>57881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90668</t>
+          <t>90202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129531</t>
+          <t>130778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174662</t>
+          <t>176779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>638608</t>
+          <t>640033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>674248</t>
+          <t>672296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>685625</t>
+          <t>686091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>719907</t>
+          <t>718412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1337747</t>
+          <t>1335630</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1382878</t>
+          <t>1381631</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>470835</t>
+          <t>471293</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>553488</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>380482</t>
+          <t>384174</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>456084</t>
+          <t>457603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>873613</t>
+          <t>873195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>990516</t>
+          <t>991115</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>67713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>52888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75103</t>
+          <t>73492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113980</t>
+          <t>112425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224810</t>
+          <t>227025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251903</t>
+          <t>255698</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232344</t>
+          <t>231109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256977</t>
+          <t>256027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464755</t>
+          <t>466310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503632</t>
+          <t>505243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45656</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75919</t>
+          <t>75964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>37321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66974</t>
+          <t>65174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90965</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131712</t>
+          <t>134524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422538</t>
+          <t>422493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452801</t>
+          <t>451021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446356</t>
+          <t>448156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474635</t>
+          <t>476009</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>880075</t>
+          <t>877263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920822</t>
+          <t>919499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81735</t>
+          <t>82729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115301</t>
+          <t>114529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43834</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134303</t>
+          <t>132944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175365</t>
+          <t>179374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207810</t>
+          <t>208582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>241376</t>
+          <t>240382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266965</t>
+          <t>267565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>294902</t>
+          <t>296314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>486482</t>
+          <t>482473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527544</t>
+          <t>528903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33059</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44542</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>61923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95057</t>
+          <t>98071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308946</t>
+          <t>308204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335643</t>
+          <t>334156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339166</t>
+          <t>339433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361503</t>
+          <t>363345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657353</t>
+          <t>654339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691774</t>
+          <t>690487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>34509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60785</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178778</t>
+          <t>178606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197319</t>
+          <t>197492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184445</t>
+          <t>184476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201812</t>
+          <t>202753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370426</t>
+          <t>369235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395394</t>
+          <t>396702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>105784</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>50662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80432</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135201</t>
+          <t>135454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178364</t>
+          <t>179637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166177</t>
+          <t>166296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196805</t>
+          <t>198829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199599</t>
+          <t>201083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227702</t>
+          <t>229369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373747</t>
+          <t>372474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416910</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>148694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190360</t>
+          <t>193164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125558</t>
+          <t>128953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170181</t>
+          <t>174170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>285913</t>
+          <t>287466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351750</t>
+          <t>351626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>469472</t>
+          <t>466668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>513695</t>
+          <t>511138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>520497</t>
+          <t>516508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>565120</t>
+          <t>561725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>998760</t>
+          <t>998884</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1064597</t>
+          <t>1063044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>44979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73670</t>
+          <t>73405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>46777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76055</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>96387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140177</t>
+          <t>138597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>695840</t>
+          <t>696105</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724319</t>
+          <t>724531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738299</t>
+          <t>739372</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>768596</t>
+          <t>767577</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1443687</t>
+          <t>1445267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1484499</t>
+          <t>1487477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>551193</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>642646</t>
+          <t>641753</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>430882</t>
+          <t>431953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>516401</t>
+          <t>515392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1015275</t>
+          <t>1012265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1135391</t>
+          <t>1136203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2756401</t>
+          <t>2757294</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2845146</t>
+          <t>2847854</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3007026</t>
+          <t>3008035</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3092545</t>
+          <t>3091474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5787084</t>
+          <t>5786272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5907200</t>
+          <t>5910210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72155</t>
+          <t>73171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54772</t>
+          <t>55682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82457</t>
+          <t>82418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121120</t>
+          <t>121272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221606</t>
+          <t>220590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250716</t>
+          <t>250007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233021</t>
+          <t>232111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257028</t>
+          <t>256728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460434</t>
+          <t>460282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499097</t>
+          <t>499136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78498</t>
+          <t>79394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60346</t>
+          <t>61570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94464</t>
+          <t>93463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117606</t>
+          <t>120048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162077</t>
+          <t>162966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>419880</t>
+          <t>418984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447434</t>
+          <t>448572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426426</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460544</t>
+          <t>459320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>857191</t>
+          <t>856302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901662</t>
+          <t>899220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53916</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>56178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87047</t>
+          <t>86710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275833</t>
+          <t>275117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295411</t>
+          <t>296029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279156</t>
+          <t>279118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302283</t>
+          <t>302623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561411</t>
+          <t>561748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593216</t>
+          <t>592280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65131</t>
+          <t>66979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57298</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>75828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>115869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303867</t>
+          <t>302019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331379</t>
+          <t>331061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328076</t>
+          <t>327748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352304</t>
+          <t>353244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>640905</t>
+          <t>638503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678438</t>
+          <t>678544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197001</t>
+          <t>196430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207906</t>
+          <t>208347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214426</t>
+          <t>214148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413620</t>
+          <t>414479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426124</t>
+          <t>426213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250026</t>
+          <t>250154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252955</t>
+          <t>253071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266238</t>
+          <t>266155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507481</t>
+          <t>507404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>524226</t>
+          <t>523576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73307</t>
+          <t>75683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111475</t>
+          <t>113355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91113</t>
+          <t>92091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130296</t>
+          <t>130246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174795</t>
+          <t>174313</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>231293</t>
+          <t>230668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>532630</t>
+          <t>530750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>570798</t>
+          <t>568422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547241</t>
+          <t>547291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>586424</t>
+          <t>585446</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1090349</t>
+          <t>1090974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1146847</t>
+          <t>1147329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126636</t>
+          <t>125906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170133</t>
+          <t>170315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129518</t>
+          <t>131999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174595</t>
+          <t>176449</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269897</t>
+          <t>269709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331985</t>
+          <t>332293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>601138</t>
+          <t>600956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>644635</t>
+          <t>645365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>648257</t>
+          <t>646403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>693334</t>
+          <t>690853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1262138</t>
+          <t>1261830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1324226</t>
+          <t>1324414</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>417035</t>
+          <t>411298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>500918</t>
+          <t>496714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,47 +10138,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>477446</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>436026</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>517030</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>12,39%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>477446</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>437175</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>516935</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>870594</t>
+          <t>876401</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>993009</t>
+          <t>986589</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2864354</t>
+          <t>2868558</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2948237</t>
+          <t>2953974</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,49 +10251,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3040762</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3001178</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3082182</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>87,61%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3040762</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3001273</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3081033</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>5633</t>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5890471</t>
+          <t>5896891</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6012886</t>
+          <t>6007079</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,97 +10702,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>513</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2595</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287501</t>
+          <t>287048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598482</t>
+          <t>598144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69979</t>
+          <t>69275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115797</t>
+          <t>115672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66111</t>
+          <t>65124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97299</t>
+          <t>96744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144811</t>
+          <t>144861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202299</t>
+          <t>201942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401181</t>
+          <t>401306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446999</t>
+          <t>447703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417077</t>
+          <t>417632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448265</t>
+          <t>449252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829054</t>
+          <t>829411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886542</t>
+          <t>886492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61106</t>
+          <t>61345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285285</t>
+          <t>285450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302654</t>
+          <t>302260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312082</t>
+          <t>310029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331773</t>
+          <t>330631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603473</t>
+          <t>603234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630082</t>
+          <t>631032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>73675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57984</t>
+          <t>57193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>62991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118848</t>
+          <t>119893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237409</t>
+          <t>236538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>417734</t>
+          <t>418525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449985</t>
+          <t>450414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667083</t>
+          <t>666038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722629</t>
+          <t>722940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27611</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>162117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173163</t>
+          <t>173098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193269</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203757</t>
+          <t>203593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359405</t>
+          <t>359536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375081</t>
+          <t>374401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>47595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75560</t>
+          <t>74053</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62225</t>
+          <t>64361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87452</t>
+          <t>87478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119911</t>
+          <t>117795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>154204</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193277</t>
+          <t>194784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221126</t>
+          <t>221242</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169604</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194831</t>
+          <t>192695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371168</t>
+          <t>371689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405982</t>
+          <t>408098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63022</t>
+          <t>64436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105825</t>
+          <t>107257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119795</t>
+          <t>122663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103074</t>
+          <t>106895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210754</t>
+          <t>209573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>516322</t>
+          <t>514890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559125</t>
+          <t>557711</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>729308</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>809379</t>
+          <t>807855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1260495</t>
+          <t>1261676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1368175</t>
+          <t>1364354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98273</t>
+          <t>108380</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>311227</t>
+          <t>312986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111204</t>
+          <t>113413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148353</t>
+          <t>149480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211272</t>
+          <t>218017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>425419</t>
+          <t>425338</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>617493</t>
+          <t>615734</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>830447</t>
+          <t>820340</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567479</t>
+          <t>566352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>604628</t>
+          <t>602419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1219134</t>
+          <t>1219215</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1433281</t>
+          <t>1426536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>427918</t>
+          <t>415959</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>596289</t>
+          <t>602016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>371769</t>
+          <t>367559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>501114</t>
+          <t>499047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>856184</t>
+          <t>850031</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1066815</t>
+          <t>1071214</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2856241</t>
+          <t>2850514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3024612</t>
+          <t>3036571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3158006</t>
+          <t>3160073</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3287351</t>
+          <t>3291561</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6044835</t>
+          <t>6040436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6255466</t>
+          <t>6261619</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51642</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>90334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226680</t>
+          <t>227101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249607</t>
+          <t>248426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209196</t>
+          <t>210134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233387</t>
+          <t>233287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445770</t>
+          <t>443514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475447</t>
+          <t>475671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99923</t>
+          <t>100325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138431</t>
+          <t>137691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84156</t>
+          <t>84754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120225</t>
+          <t>121098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192982</t>
+          <t>194120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246278</t>
+          <t>248582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354644</t>
+          <t>355384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393152</t>
+          <t>392750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383724</t>
+          <t>382851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>419793</t>
+          <t>419195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750746</t>
+          <t>748442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804042</t>
+          <t>802904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>51428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94123</t>
+          <t>96420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266094</t>
+          <t>266486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289027</t>
+          <t>289469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>283984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>306346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560135</t>
+          <t>557838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>591454</t>
+          <t>590896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>67117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99075</t>
+          <t>98318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>59897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109359</t>
+          <t>108529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259596</t>
+          <t>260353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>291541</t>
+          <t>291554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310777</t>
+          <t>311559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335782</t>
+          <t>336225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580193</t>
+          <t>580537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620768</t>
+          <t>621598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183969</t>
+          <t>183396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>197243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187278</t>
+          <t>185689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200100</t>
+          <t>199744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376243</t>
+          <t>376045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394474</t>
+          <t>394428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>54438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83963</t>
+          <t>84183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>34496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>59212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>96307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137397</t>
+          <t>134404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186848</t>
+          <t>186628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216259</t>
+          <t>216373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220060</t>
+          <t>218932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243046</t>
+          <t>243648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>411558</t>
+          <t>414551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452309</t>
+          <t>452648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64423</t>
+          <t>63182</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99246</t>
+          <t>96228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48879</t>
+          <t>48444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119284</t>
+          <t>122780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166738</t>
+          <t>168166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>515781</t>
+          <t>518799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>550604</t>
+          <t>551845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>558394</t>
+          <t>558847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>588360</t>
+          <t>588795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1085528</t>
+          <t>1084100</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1132982</t>
+          <t>1129486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96083</t>
+          <t>95481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57881</t>
+          <t>57486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>93237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130778</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176779</t>
+          <t>174951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>640033</t>
+          <t>640635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>672296</t>
+          <t>673680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>686091</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>718412</t>
+          <t>718807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1335630</t>
+          <t>1337458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1381631</t>
+          <t>1383824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>471293</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>557285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>384174</t>
+          <t>380718</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>457603</t>
+          <t>459893</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>880119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>991115</t>
+          <t>988972</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67713</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52888</t>
+          <t>51456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73492</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112425</t>
+          <t>110797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227025</t>
+          <t>224441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255698</t>
+          <t>253441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231109</t>
+          <t>232541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256027</t>
+          <t>257167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>466310</t>
+          <t>467938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>505243</t>
+          <t>504140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75964</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37321</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92288</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134524</t>
+          <t>133655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422493</t>
+          <t>421645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>451450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448156</t>
+          <t>448388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476009</t>
+          <t>475646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877263</t>
+          <t>878132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919499</t>
+          <t>918383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82729</t>
+          <t>81788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114529</t>
+          <t>114998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42422</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>72625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132944</t>
+          <t>131215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179374</t>
+          <t>177890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208582</t>
+          <t>208113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>240382</t>
+          <t>241323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267565</t>
+          <t>266111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296314</t>
+          <t>294669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>482473</t>
+          <t>483957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>528903</t>
+          <t>530632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60498</t>
+          <t>60003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>44601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>96522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308204</t>
+          <t>308699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334156</t>
+          <t>335335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339433</t>
+          <t>339107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363345</t>
+          <t>362706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654339</t>
+          <t>655888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>690487</t>
+          <t>692319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178606</t>
+          <t>179337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197492</t>
+          <t>197393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184476</t>
+          <t>184867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202753</t>
+          <t>203331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396702</t>
+          <t>395433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105784</t>
+          <t>106640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>51596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78948</t>
+          <t>81295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179637</t>
+          <t>176541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166296</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198829</t>
+          <t>196286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201083</t>
+          <t>198736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229369</t>
+          <t>228435</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372474</t>
+          <t>375570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416657</t>
+          <t>416239</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148694</t>
+          <t>147089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>193164</t>
+          <t>193629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128953</t>
+          <t>128140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174170</t>
+          <t>172543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>287466</t>
+          <t>288498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351626</t>
+          <t>350415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>466668</t>
+          <t>466203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>511138</t>
+          <t>512743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>516508</t>
+          <t>518135</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561725</t>
+          <t>562538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>998884</t>
+          <t>1000095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1063044</t>
+          <t>1062012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73405</t>
+          <t>75085</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46777</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96387</t>
+          <t>99265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138597</t>
+          <t>141086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696105</t>
+          <t>694425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724531</t>
+          <t>726225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>739372</t>
+          <t>740229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>767577</t>
+          <t>769218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1445267</t>
+          <t>1442778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1487477</t>
+          <t>1484599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>551193</t>
+          <t>551494</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>641753</t>
+          <t>643560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>431953</t>
+          <t>438102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>515392</t>
+          <t>517413</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1012265</t>
+          <t>1012196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1136203</t>
+          <t>1131831</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73171</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82418</t>
+          <t>79946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121272</t>
+          <t>117082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220590</t>
+          <t>220130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>249192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232111</t>
+          <t>233579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256728</t>
+          <t>256287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460282</t>
+          <t>464472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499136</t>
+          <t>501608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49806</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79394</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61570</t>
+          <t>62179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93463</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120048</t>
+          <t>117697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162966</t>
+          <t>164478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418984</t>
+          <t>417509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448572</t>
+          <t>448053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>425968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459320</t>
+          <t>458711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>856302</t>
+          <t>854790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899220</t>
+          <t>901571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40269</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>56532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>87397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>275241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296029</t>
+          <t>295282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279118</t>
+          <t>279603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302623</t>
+          <t>302583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561748</t>
+          <t>561061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592280</t>
+          <t>591926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>39082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66979</t>
+          <t>66162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>57975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75828</t>
+          <t>78633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115869</t>
+          <t>116568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302019</t>
+          <t>302836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331061</t>
+          <t>329916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327748</t>
+          <t>327399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353244</t>
+          <t>353641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638503</t>
+          <t>637804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678544</t>
+          <t>675739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196430</t>
+          <t>197016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214148</t>
+          <t>214387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414479</t>
+          <t>413872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426213</t>
+          <t>426180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250154</t>
+          <t>250015</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260088</t>
+          <t>260109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253071</t>
+          <t>253814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266155</t>
+          <t>266217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507404</t>
+          <t>506733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523576</t>
+          <t>523553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75683</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113355</t>
+          <t>114748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92091</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130246</t>
+          <t>129397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174313</t>
+          <t>176207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>230668</t>
+          <t>230195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>530750</t>
+          <t>529357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>568422</t>
+          <t>568521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547291</t>
+          <t>548140</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>585446</t>
+          <t>587031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1090974</t>
+          <t>1091447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1147329</t>
+          <t>1145435</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>125906</t>
+          <t>126844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170315</t>
+          <t>171727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131999</t>
+          <t>131863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176449</t>
+          <t>176733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269709</t>
+          <t>265534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332293</t>
+          <t>329638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600956</t>
+          <t>599544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>645365</t>
+          <t>644427</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>646403</t>
+          <t>646119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690853</t>
+          <t>690989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1261830</t>
+          <t>1264485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1324414</t>
+          <t>1328589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>411298</t>
+          <t>411999</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>496714</t>
+          <t>493086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>436026</t>
+          <t>437319</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>517030</t>
+          <t>520957</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>876401</t>
+          <t>876199</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>986589</t>
+          <t>990913</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10845,27 +10845,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289122</t>
+          <t>315568</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287048</t>
+          <t>313535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>600564</t>
+          <t>634413</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598144</t>
+          <t>632453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90694</t>
+          <t>90766</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69275</t>
+          <t>71862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115672</t>
+          <t>114623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65124</t>
+          <t>69616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96744</t>
+          <t>102020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>171974</t>
+          <t>175576</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144861</t>
+          <t>149779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201942</t>
+          <t>204214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426284</t>
+          <t>438525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401306</t>
+          <t>414668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447703</t>
+          <t>457429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>433095</t>
+          <t>461076</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417632</t>
+          <t>443866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449252</t>
+          <t>476270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>859379</t>
+          <t>899601</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829411</t>
+          <t>870963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886492</t>
+          <t>925398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516978</t>
+          <t>529291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514376</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1075177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39099</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33547</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>63518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>293779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285450</t>
+          <t>283090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302260</t>
+          <t>301812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322335</t>
+          <t>329687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310029</t>
+          <t>318002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330631</t>
+          <t>338042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>618027</t>
+          <t>623466</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603234</t>
+          <t>608247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631032</t>
+          <t>634459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315451</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664579</t>
+          <t>671765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>54788</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>76797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>60424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>88222</t>
+          <t>101806</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62991</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119893</t>
+          <t>130835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>264562</t>
+          <t>315866</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236538</t>
+          <t>293857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279108</t>
+          <t>333619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>433147</t>
+          <t>374943</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>418525</t>
+          <t>361537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450414</t>
+          <t>386177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>697709</t>
+          <t>690810</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666038</t>
+          <t>661781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722940</t>
+          <t>711967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>785931</t>
+          <t>792616</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>168904</t>
+          <t>193374</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162117</t>
+          <t>185332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173098</t>
+          <t>198203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>199660</t>
+          <t>218386</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191672</t>
+          <t>210634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203593</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>368564</t>
+          <t>411760</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359536</t>
+          <t>401504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374401</t>
+          <t>418749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60279</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47595</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74053</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75354</t>
+          <t>77082</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>66251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87478</t>
+          <t>91298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>135633</t>
+          <t>134872</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117795</t>
+          <t>119942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154204</t>
+          <t>152165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>208558</t>
+          <t>212118</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194784</t>
+          <t>198486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221242</t>
+          <t>223406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>181702</t>
+          <t>186668</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169578</t>
+          <t>172452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192695</t>
+          <t>197499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>390260</t>
+          <t>398786</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371689</t>
+          <t>381493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408098</t>
+          <t>413716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>533658</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>103965</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64436</t>
+          <t>82113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107257</t>
+          <t>129975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>85871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122663</t>
+          <t>128506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>169384</t>
+          <t>208457</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106895</t>
+          <t>180967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209573</t>
+          <t>242163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>537817</t>
+          <t>613484</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>514890</t>
+          <t>587474</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>557711</t>
+          <t>635336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>764048</t>
+          <t>666127</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>726440</t>
+          <t>642113</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>807855</t>
+          <t>684748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1301865</t>
+          <t>1279611</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1261676</t>
+          <t>1245905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1364354</t>
+          <t>1307101</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622147</t>
+          <t>717449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849103</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471249</t>
+          <t>1488068</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>221466</t>
+          <t>256996</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108380</t>
+          <t>231948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>312986</t>
+          <t>287968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>130263</t>
+          <t>148362</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113413</t>
+          <t>129455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149480</t>
+          <t>169831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>351729</t>
+          <t>405358</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218017</t>
+          <t>369567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>425338</t>
+          <t>440911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>707254</t>
+          <t>541076</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>615734</t>
+          <t>510104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>820340</t>
+          <t>566124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>585569</t>
+          <t>680814</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>566352</t>
+          <t>659345</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>602419</t>
+          <t>699721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1292824</t>
+          <t>1221890</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1219215</t>
+          <t>1186337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1426536</t>
+          <t>1257681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715832</t>
+          <t>829176</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644553</t>
+          <t>1627248</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>415959</t>
+          <t>546737</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>602016</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>367559</t>
+          <t>459725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>499047</t>
+          <t>538703</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>850031</t>
+          <t>1034481</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1071214</t>
+          <t>1166270</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
